--- a/Data/EXCEL/Transfer/salemon/202412/4803-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/4803-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A87DE349-5827-4F68-BD84-C413B88E244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44D4BAA7-C693-407D-B91F-7B9B6A964A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{EA97B0AB-4532-4BEA-88CB-DC3FEE9D07AB}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{9DF98A49-FDAC-493F-8D6F-16F0DF7CC07D}"/>
   </bookViews>
   <sheets>
     <sheet name="4803-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,23 +1255,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E930AE-5135-4F95-92B2-7150DEE61974}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF52582-6019-402B-BAB2-D4FBA7DD5578}">
   <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" customWidth="1"/>
-    <col min="2" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
-    <col min="9" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.36328125" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
-    <col min="13" max="13" width="15.36328125" customWidth="1"/>
-    <col min="14" max="15" width="14.54296875" customWidth="1"/>
-    <col min="16" max="16" width="15.36328125" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="9" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10.125" customWidth="1"/>
+    <col min="12" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="13" width="10.125" customWidth="1"/>
+    <col min="14" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="10.125" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1380,7 +1380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44593</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>-37.200000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>44562</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44531</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>-13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>44501</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44470</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>-9.01</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>44440</v>
       </c>
